--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="429">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:19:25+00:00</t>
+    <t>2026-10-13T06:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -722,6 +722,12 @@
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.type</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.system</t>
@@ -1073,6 +1079,10 @@
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>ORC-24, STF-11, ROL-11, PRT-14</t>
@@ -1675,7 +1685,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="46.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -4387,9 +4397,11 @@
       <c r="X24" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y24" s="2"/>
+      <c r="Y24" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4436,7 +4448,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>187</v>
@@ -4465,7 +4477,7 @@
         <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>189</v>
@@ -4481,7 +4493,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -4552,7 +4564,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>197</v>
@@ -4581,7 +4593,7 @@
         <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>199</v>
@@ -4666,7 +4678,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>206</v>
@@ -4778,7 +4790,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>214</v>
@@ -4892,10 +4904,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5004,10 +5016,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5118,10 +5130,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5147,13 +5159,13 @@
         <v>157</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5203,7 +5215,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5212,7 +5224,7 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
@@ -5232,10 +5244,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5261,13 +5273,13 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5296,10 +5308,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5317,7 +5329,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5346,10 +5358,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5375,13 +5387,13 @@
         <v>146</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5431,7 +5443,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5449,7 +5461,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5460,10 +5472,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5489,13 +5501,13 @@
         <v>157</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5503,7 +5515,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>21</v>
@@ -5545,7 +5557,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5574,13 +5586,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
@@ -5690,7 +5702,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>156</v>
@@ -5802,7 +5814,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>162</v>
@@ -5916,7 +5928,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>167</v>
@@ -6032,7 +6044,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>177</v>
@@ -6097,9 +6109,11 @@
       <c r="X39" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y39" s="2"/>
+      <c r="Y39" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6146,7 +6160,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>187</v>
@@ -6175,7 +6189,7 @@
         <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M40" t="s" s="2">
         <v>189</v>
@@ -6191,7 +6205,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>21</v>
@@ -6262,7 +6276,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>197</v>
@@ -6376,7 +6390,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>206</v>
@@ -6488,7 +6502,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>214</v>
@@ -6602,10 +6616,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6714,10 +6728,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6828,10 +6842,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6857,13 +6871,13 @@
         <v>157</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6913,7 +6927,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6922,7 +6936,7 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
@@ -6942,10 +6956,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6971,13 +6985,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7006,10 +7020,10 @@
         <v>183</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7027,7 +7041,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7056,10 +7070,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7085,13 +7099,13 @@
         <v>146</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7141,7 +7155,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7159,7 +7173,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7170,10 +7184,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7199,13 +7213,13 @@
         <v>157</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7213,7 +7227,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>21</v>
@@ -7255,7 +7269,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7284,13 +7298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>21</v>
@@ -7400,7 +7414,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>156</v>
@@ -7512,7 +7526,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>162</v>
@@ -7626,7 +7640,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>167</v>
@@ -7742,7 +7756,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>177</v>
@@ -7807,9 +7821,11 @@
       <c r="X54" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y54" s="2"/>
+      <c r="Y54" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7856,7 +7872,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>187</v>
@@ -7885,7 +7901,7 @@
         <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>189</v>
@@ -7901,7 +7917,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>21</v>
@@ -7972,7 +7988,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>197</v>
@@ -8086,7 +8102,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>206</v>
@@ -8198,7 +8214,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>214</v>
@@ -8312,10 +8328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8424,10 +8440,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8538,10 +8554,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8567,13 +8583,13 @@
         <v>157</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8623,7 +8639,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8632,7 +8648,7 @@
         <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>100</v>
@@ -8652,10 +8668,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8681,13 +8697,13 @@
         <v>102</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8716,10 +8732,10 @@
         <v>183</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -8737,7 +8753,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8766,10 +8782,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8795,13 +8811,13 @@
         <v>146</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8851,7 +8867,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8869,7 +8885,7 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
@@ -8880,10 +8896,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8909,13 +8925,13 @@
         <v>157</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8923,7 +8939,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>21</v>
@@ -8965,7 +8981,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8994,10 +9010,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9020,70 +9036,70 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q65" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="R65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9101,21 +9117,21 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9138,19 +9154,19 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9199,7 +9215,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9214,13 +9230,13 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9228,10 +9244,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9254,19 +9270,19 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9315,7 +9331,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9330,13 +9346,13 @@
         <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9344,10 +9360,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9370,19 +9386,19 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9431,7 +9447,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9443,16 +9459,16 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>100</v>
+        <v>342</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9460,10 +9476,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9489,14 +9505,14 @@
         <v>108</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9524,10 +9540,10 @@
         <v>172</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9545,7 +9561,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9560,13 +9576,13 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -9574,10 +9590,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9603,10 +9619,10 @@
         <v>157</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9686,10 +9702,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9715,10 +9731,10 @@
         <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9796,13 +9812,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="B72" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="C72" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>21</v>
@@ -9824,13 +9840,13 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9890,7 +9906,7 @@
         <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>139</v>
@@ -9910,10 +9926,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9939,10 +9955,10 @@
         <v>157</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9993,7 +10009,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10022,10 +10038,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10048,17 +10064,17 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10107,7 +10123,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10122,13 +10138,13 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10136,10 +10152,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10162,17 +10178,17 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10221,7 +10237,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10239,10 +10255,10 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10250,10 +10266,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10276,13 +10292,13 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10333,7 +10349,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10348,13 +10364,13 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10362,10 +10378,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10474,10 +10490,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10588,14 +10604,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10617,10 +10633,10 @@
         <v>134</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>137</v>
@@ -10675,7 +10691,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10704,10 +10720,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10733,14 +10749,14 @@
         <v>146</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -10789,7 +10805,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10807,7 +10823,7 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
@@ -10818,10 +10834,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10847,10 +10863,10 @@
         <v>178</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10877,31 +10893,31 @@
         <v>21</v>
       </c>
       <c r="X81" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>88</v>
@@ -10919,10 +10935,10 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -10930,10 +10946,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10959,14 +10975,14 @@
         <v>207</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11015,7 +11031,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11033,10 +11049,10 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -11044,10 +11060,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11073,10 +11089,10 @@
         <v>215</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11127,7 +11143,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11145,7 +11161,7 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
@@ -11156,10 +11172,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11185,16 +11201,16 @@
         <v>178</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11243,7 +11259,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11258,13 +11274,13 @@
         <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2851" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T06:32:12+00:00</t>
+    <t>2026-10-13T12:58:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -933,10 +933,10 @@
     <t>Practitioner.identifier:vbPK.system</t>
   </si>
   <si>
-    <t>OID for the vbPK in Austria</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.40.0.34.4.22</t>
+    <t>OID for the specific vbPK in Austria</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/core/r4/ValueSet/at-core-vbpk</t>
   </si>
   <si>
     <t>Practitioner.identifier:vbPK.value</t>
@@ -946,27 +946,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:vbPK.assigner</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.id</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.reference</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.type</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:vbPK.assigner.display</t>
-  </si>
-  <si>
-    <t>Bundesministerium für Inneres</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -1658,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN84"/>
+  <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.5625" customWidth="true" bestFit="true"/>
@@ -7314,7 +7293,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -7917,7 +7896,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>21</v>
@@ -7935,13 +7914,11 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8331,7 +8308,7 @@
         <v>302</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>239</v>
+        <v>302</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8351,23 +8328,29 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>303</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>158</v>
+        <v>304</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="R59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8411,7 +8394,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>160</v>
+        <v>302</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8423,31 +8406,31 @@
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>161</v>
+        <v>309</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>21</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>241</v>
+        <v>311</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8463,21 +8446,23 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>312</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>135</v>
+        <v>313</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8513,19 +8498,19 @@
         <v>21</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>166</v>
+        <v>311</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8537,16 +8522,16 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>161</v>
+        <v>318</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>21</v>
+        <v>319</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8554,10 +8539,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>243</v>
+        <v>320</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8568,7 +8553,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8580,18 +8565,20 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>157</v>
+        <v>321</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>244</v>
+        <v>322</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>245</v>
+        <v>323</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8639,28 +8626,28 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>247</v>
+        <v>320</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>131</v>
+        <v>327</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -8668,10 +8655,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8682,7 +8669,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -8694,18 +8681,20 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>102</v>
+        <v>330</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>251</v>
+        <v>331</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>252</v>
+        <v>332</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8729,13 +8718,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -8753,28 +8742,28 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>335</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>131</v>
+        <v>337</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -8782,10 +8771,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>258</v>
+        <v>339</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8808,18 +8797,18 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8843,13 +8832,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -8867,7 +8856,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>262</v>
+        <v>339</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8882,13 +8871,13 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>263</v>
+        <v>346</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -8896,10 +8885,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>265</v>
+        <v>348</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8919,27 +8908,25 @@
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>157</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>266</v>
+        <v>349</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>21</v>
@@ -8981,7 +8968,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>270</v>
+        <v>160</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8993,13 +8980,13 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
@@ -9010,10 +8997,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>309</v>
+        <v>351</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>309</v>
+        <v>351</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9024,7 +9011,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9033,29 +9020,23 @@
         <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>310</v>
+        <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9087,53 +9068,53 @@
         <v>21</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="AC65" s="2"/>
       <c r="AD65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>309</v>
+        <v>166</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>316</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>317</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9142,7 +9123,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -9151,23 +9132,19 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9215,7 +9192,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>318</v>
+        <v>166</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9224,19 +9201,19 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>326</v>
+        <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9244,10 +9221,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9258,7 +9235,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9267,23 +9244,19 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>328</v>
+        <v>157</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9331,28 +9304,28 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>335</v>
+        <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9360,10 +9333,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9374,7 +9347,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -9386,19 +9359,17 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>337</v>
+        <v>364</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9447,28 +9418,28 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>342</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9476,10 +9447,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9490,7 +9461,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -9499,20 +9470,20 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>372</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9537,13 +9508,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>351</v>
+        <v>21</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9561,13 +9532,13 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
@@ -9576,13 +9547,13 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -9590,10 +9561,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9604,7 +9575,7 @@
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -9616,13 +9587,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>157</v>
+        <v>379</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9673,28 +9644,28 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>160</v>
+        <v>378</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -9702,10 +9673,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9716,7 +9687,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -9728,13 +9699,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>359</v>
+        <v>158</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>360</v>
+        <v>159</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9773,35 +9744,37 @@
         <v>21</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AC71" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>21</v>
@@ -9812,23 +9785,21 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
@@ -9840,15 +9811,17 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>363</v>
+        <v>134</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>364</v>
+        <v>135</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -9906,7 +9879,7 @@
         <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>139</v>
@@ -9915,7 +9888,7 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
@@ -9926,42 +9899,46 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -10009,25 +9986,25 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
@@ -10038,10 +10015,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10052,7 +10029,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
@@ -10061,20 +10038,20 @@
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>371</v>
+        <v>146</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10123,13 +10100,13 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
@@ -10138,13 +10115,13 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>377</v>
+        <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10152,10 +10129,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10163,10 +10140,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10178,18 +10155,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>379</v>
+        <v>178</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>382</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
@@ -10213,13 +10188,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>21</v>
+        <v>400</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -10237,13 +10212,13 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
@@ -10258,7 +10233,7 @@
         <v>383</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10266,10 +10241,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10280,7 +10255,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10292,16 +10267,18 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>386</v>
+        <v>207</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10349,13 +10326,13 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
@@ -10364,13 +10341,13 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10378,10 +10355,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10404,13 +10381,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>158</v>
+        <v>411</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>159</v>
+        <v>412</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10461,7 +10438,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>160</v>
+        <v>410</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10473,13 +10450,13 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>161</v>
+        <v>413</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
@@ -10490,14 +10467,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10516,18 +10493,20 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>135</v>
+        <v>415</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>163</v>
+        <v>416</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -10551,13 +10530,13 @@
         <v>21</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -10575,7 +10554,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>166</v>
+        <v>414</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10587,702 +10566,18 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>161</v>
+        <v>420</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>21</v>
+        <v>421</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AN84" t="s" s="2">
         <v>21</v>
       </c>
     </row>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:58:59+00:00</t>
+    <t>2026-10-19T05:20:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T05:20:34+00:00</t>
+    <t>2026-10-19T13:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4472,10 +4472,10 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S25" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>192</v>
@@ -5494,10 +5494,10 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S34" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>21</v>
@@ -6184,10 +6184,10 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S40" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>192</v>
@@ -7206,10 +7206,10 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S49" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>21</v>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2851" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2851" uniqueCount="428">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:05:38+00:00</t>
+    <t>2026-10-20T07:19:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -712,6 +712,12 @@
     <t>GDA-OID</t>
   </si>
   <si>
+    <t>Gesundheitsdiensteanbieter-OID (GDA-OID)</t>
+  </si>
+  <si>
+    <t>The OID of the healthcare service provider (Gesundheitsdiensteanbieter, GDA) as registered in the Austrian GDA-Index. The OID is assigned by the Federal Ministry of Health (Bundesministerium für Gesundheit).</t>
+  </si>
+  <si>
     <t>Practitioner.identifier:GDA-OID.id</t>
   </si>
   <si>
@@ -733,7 +739,7 @@
     <t>Practitioner.identifier:GDA-OID.system</t>
   </si>
   <si>
-    <t>A GDA in Austria is represented via an URI (OID)</t>
+    <t>A Gesundheitsdiensteanbieter (GDA) in Austria is represented via a URI (OID)</t>
   </si>
   <si>
     <t>urn:ietf:rfc:3986</t>
@@ -742,7 +748,7 @@
     <t>Practitioner.identifier:GDA-OID.value</t>
   </si>
   <si>
-    <t>OID for the GDA in Austria</t>
+    <t>OID for the Gesundheitsdiensteanbieter (GDA) in Austria</t>
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.period</t>
@@ -861,6 +867,12 @@
     <t>VPNR</t>
   </si>
   <si>
+    <t>Vertragspartnernummer (VPNR)</t>
+  </si>
+  <si>
+    <t>The contract partner number (Vertragspartnernummer, VPNR) of the practitioner, assigned by the Federation of Austrian Social Insurances (Dachverband der österreichischen Sozialversicherungsträger).</t>
+  </si>
+  <si>
     <t>Practitioner.identifier:VPNR.id</t>
   </si>
   <si>
@@ -918,6 +930,12 @@
     <t>vbPK</t>
   </si>
   <si>
+    <t>Verschlüsseltes bereichsspezifisches Personenkennzeichen (vbPK)</t>
+  </si>
+  <si>
+    <t>The encrypted sector-specific personal identifier (Verschlüsseltes bereichsspezifisches Personenkennzeichen, vbPK) of the practitioner, used in Austrian e-Government processes. The OID of the system identifies the sector (e.g. GH for Gesundheit, SV for Sozialversicherung, AS for Amtliche Statistik) according to the E-Government-Bereichsabgrenzungsverordnung (E-Gov-BerAbgrV).</t>
+  </si>
+  <si>
     <t>Practitioner.identifier:vbPK.id</t>
   </si>
   <si>
@@ -933,7 +951,7 @@
     <t>Practitioner.identifier:vbPK.system</t>
   </si>
   <si>
-    <t>OID for the specific vbPK in Austria</t>
+    <t>OID for the specific verschlüsseltes bereichsspezifisches Personenkennzeichen (vbPK) in Austria</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/core/r4/ValueSet/at-core-vbpk</t>
@@ -1128,11 +1146,10 @@
 </t>
   </si>
   <si>
-    <t>Administrative Gender Addition</t>
-  </si>
-  <si>
-    <t>HL7® Austria FHIR® Core Extension for the administrative gender of a person (Patient, Practitioner, ...). 
-The extension is used to add the missing codes and is applied in case the code for administrative gender itself is set to 'other'.</t>
+    <t>Additional administrative gender (Geschlecht)</t>
+  </si>
+  <si>
+    <t>Additional administrative gender code (Geschlecht) required in Austria that is not covered by the FHIR administrative gender codes. The extension is only applied in case the administrative gender itself is set to 'other' (Ergänzung zu 'other').</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -3884,10 +3901,10 @@
         <v>146</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>147</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>148</v>
+        <v>226</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
@@ -3969,7 +3986,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>156</v>
@@ -4081,7 +4098,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>162</v>
@@ -4195,7 +4212,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>167</v>
@@ -4311,7 +4328,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>177</v>
@@ -4377,10 +4394,10 @@
         <v>183</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4427,7 +4444,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>187</v>
@@ -4456,7 +4473,7 @@
         <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>189</v>
@@ -4475,7 +4492,7 @@
         <v>21</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>192</v>
@@ -4543,7 +4560,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>197</v>
@@ -4572,7 +4589,7 @@
         <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>199</v>
@@ -4657,7 +4674,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>206</v>
@@ -4769,7 +4786,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>214</v>
@@ -4883,10 +4900,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4995,10 +5012,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5109,10 +5126,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5138,13 +5155,13 @@
         <v>157</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5194,7 +5211,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5203,7 +5220,7 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
@@ -5223,10 +5240,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5252,13 +5269,13 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5287,10 +5304,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5308,7 +5325,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5337,10 +5354,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5366,13 +5383,13 @@
         <v>146</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5422,7 +5439,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5440,7 +5457,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5451,10 +5468,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5480,13 +5497,13 @@
         <v>157</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5497,7 +5514,7 @@
         <v>21</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>21</v>
@@ -5536,7 +5553,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5565,13 +5582,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
@@ -5596,10 +5613,10 @@
         <v>146</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>147</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>148</v>
+        <v>276</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
@@ -5681,7 +5698,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>156</v>
@@ -5793,7 +5810,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>162</v>
@@ -5907,7 +5924,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>167</v>
@@ -6023,7 +6040,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>177</v>
@@ -6089,10 +6106,10 @@
         <v>183</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6139,7 +6156,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>187</v>
@@ -6168,7 +6185,7 @@
         <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M40" t="s" s="2">
         <v>189</v>
@@ -6187,7 +6204,7 @@
         <v>21</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>192</v>
@@ -6255,7 +6272,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>197</v>
@@ -6369,7 +6386,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>206</v>
@@ -6481,7 +6498,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>214</v>
@@ -6595,10 +6612,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6707,10 +6724,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6821,10 +6838,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6850,13 +6867,13 @@
         <v>157</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6906,7 +6923,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6915,7 +6932,7 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
@@ -6935,10 +6952,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6964,13 +6981,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6999,10 +7016,10 @@
         <v>183</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7020,7 +7037,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7049,10 +7066,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7078,13 +7095,13 @@
         <v>146</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7134,7 +7151,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7152,7 +7169,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7163,10 +7180,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7192,13 +7209,13 @@
         <v>157</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7209,7 +7226,7 @@
         <v>21</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>21</v>
@@ -7248,7 +7265,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7277,13 +7294,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>21</v>
@@ -7308,10 +7325,10 @@
         <v>146</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>147</v>
+        <v>296</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>148</v>
+        <v>297</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
@@ -7393,7 +7410,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>156</v>
@@ -7505,7 +7522,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>162</v>
@@ -7619,7 +7636,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>167</v>
@@ -7735,7 +7752,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>177</v>
@@ -7801,10 +7818,10 @@
         <v>183</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7851,7 +7868,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>187</v>
@@ -7880,7 +7897,7 @@
         <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>189</v>
@@ -7918,7 +7935,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -7965,7 +7982,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>197</v>
@@ -8079,7 +8096,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>206</v>
@@ -8191,7 +8208,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>214</v>
@@ -8305,10 +8322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8331,70 +8348,70 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q59" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="R59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="R59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8412,21 +8429,21 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8449,19 +8466,19 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8510,7 +8527,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8525,13 +8542,13 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8539,10 +8556,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8565,19 +8582,19 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8626,7 +8643,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8641,13 +8658,13 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -8655,10 +8672,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8681,19 +8698,19 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -8742,7 +8759,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8754,16 +8771,16 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -8771,10 +8788,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8800,14 +8817,14 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -8835,10 +8852,10 @@
         <v>172</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -8856,7 +8873,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8871,13 +8888,13 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -8885,10 +8902,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8914,10 +8931,10 @@
         <v>157</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8997,10 +9014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9026,10 +9043,10 @@
         <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9107,13 +9124,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
@@ -9135,13 +9152,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9201,7 +9218,7 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>139</v>
@@ -9221,10 +9238,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9250,10 +9267,10 @@
         <v>157</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9304,7 +9321,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9333,10 +9350,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9359,17 +9376,17 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9418,7 +9435,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9433,13 +9450,13 @@
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9447,10 +9464,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9473,17 +9490,17 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9532,7 +9549,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9550,10 +9567,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -9561,10 +9578,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9587,13 +9604,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9644,7 +9661,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9659,13 +9676,13 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -9673,10 +9690,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9785,10 +9802,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9899,14 +9916,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -9928,10 +9945,10 @@
         <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>137</v>
@@ -9986,7 +10003,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10015,10 +10032,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10044,14 +10061,14 @@
         <v>146</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10100,7 +10117,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10118,7 +10135,7 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
@@ -10129,10 +10146,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10158,10 +10175,10 @@
         <v>178</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10188,13 +10205,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -10212,7 +10229,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>88</v>
@@ -10230,10 +10247,10 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10241,10 +10258,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10270,14 +10287,14 @@
         <v>207</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10326,7 +10343,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10344,10 +10361,10 @@
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10355,10 +10372,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10384,10 +10401,10 @@
         <v>215</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10438,7 +10455,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10456,7 +10473,7 @@
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
@@ -10467,10 +10484,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10496,16 +10513,16 @@
         <v>178</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10554,7 +10571,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10569,13 +10586,13 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
